--- a/results/Cost/Cost_Summerize.xlsx
+++ b/results/Cost/Cost_Summerize.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\项目\2025-ThirdPaper\结果图\经济\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\项目\2025-ThirdPaper\结果图\Cost\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77AB1D36-2051-47D4-B536-DE59A3DB4285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F1579D-5ED4-4027-AC2E-8EDE5A2BFD98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>VQC</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -71,15 +71,51 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>DQM_Seed2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Classical_Seed2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>VQC_Seed2</t>
+    <t>DQM_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Classical_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VQC_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DQM_2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Classical_2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VQC_2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DQM_3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Classical_3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VQC_3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DQM_4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Classical_4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VQC_4</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -133,11 +169,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -407,14 +449,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.36328125" customWidth="1"/>
     <col min="2" max="7" width="12.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
@@ -424,17 +466,45 @@
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -447,17 +517,44 @@
       <c r="D2">
         <v>124.78</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="3">
         <v>153.262</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="3">
         <v>92.780799999999999</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="3">
         <v>129.68899999999999</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="3">
+        <v>118.60599999999999</v>
+      </c>
+      <c r="I2" s="3">
+        <v>128.53</v>
+      </c>
+      <c r="J2" s="3">
+        <v>138.84399999999999</v>
+      </c>
+      <c r="K2" s="3">
+        <v>154.24</v>
+      </c>
+      <c r="L2" s="3">
+        <v>136.17699999999999</v>
+      </c>
+      <c r="M2" s="3">
+        <v>131.95699999999999</v>
+      </c>
+      <c r="N2">
+        <v>153.87100000000001</v>
+      </c>
+      <c r="O2">
+        <v>149.423</v>
+      </c>
+      <c r="P2">
+        <v>136.417</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -470,17 +567,44 @@
       <c r="D3">
         <v>42.416200000000003</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="3">
         <v>68.846299999999999</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="3">
         <v>48.872700000000002</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="3">
         <v>42.671700000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" s="3">
+        <v>47.878100000000003</v>
+      </c>
+      <c r="I3" s="3">
+        <v>52.901699999999998</v>
+      </c>
+      <c r="J3" s="3">
+        <v>54.332900000000002</v>
+      </c>
+      <c r="K3" s="3">
+        <v>47.7577</v>
+      </c>
+      <c r="L3" s="3">
+        <v>71.322199999999995</v>
+      </c>
+      <c r="M3" s="3">
+        <v>56.170299999999997</v>
+      </c>
+      <c r="N3">
+        <v>65.208500000000001</v>
+      </c>
+      <c r="O3">
+        <v>67.678799999999995</v>
+      </c>
+      <c r="P3">
+        <v>38.739199999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -493,17 +617,44 @@
       <c r="D4">
         <v>37.740900000000003</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="3">
         <v>43.360199999999999</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="3">
         <v>36.320799999999998</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="3">
         <v>34.635800000000003</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="3">
+        <v>28.319700000000001</v>
+      </c>
+      <c r="I4" s="3">
+        <v>38.497700000000002</v>
+      </c>
+      <c r="J4" s="3">
+        <v>4.6143000000000001</v>
+      </c>
+      <c r="K4" s="3">
+        <v>43.631500000000003</v>
+      </c>
+      <c r="L4" s="3">
+        <v>30.265999999999998</v>
+      </c>
+      <c r="M4" s="3">
+        <v>13.4512</v>
+      </c>
+      <c r="N4">
+        <v>49.279000000000003</v>
+      </c>
+      <c r="O4">
+        <v>46.764600000000002</v>
+      </c>
+      <c r="P4">
+        <v>38.450800000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -516,17 +667,44 @@
       <c r="D5">
         <v>28.831099999999999</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="3">
         <v>29.6557</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="3">
         <v>18.0808</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="3">
         <v>32.2911</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5" s="3">
+        <v>32.579000000000001</v>
+      </c>
+      <c r="I5" s="3">
+        <v>17.976299999999998</v>
+      </c>
+      <c r="J5" s="3">
+        <v>30.56</v>
+      </c>
+      <c r="K5" s="3">
+        <v>27.053599999999999</v>
+      </c>
+      <c r="L5" s="3">
+        <v>16.670500000000001</v>
+      </c>
+      <c r="M5" s="3">
+        <v>32.633800000000001</v>
+      </c>
+      <c r="N5">
+        <v>37.6402</v>
+      </c>
+      <c r="O5">
+        <v>43.491199999999999</v>
+      </c>
+      <c r="P5">
+        <v>27.352699999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -539,17 +717,44 @@
       <c r="D6">
         <v>693.14300000000003</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="3">
         <v>698.23299999999995</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="3">
         <v>642.798</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="3">
         <v>713.98699999999997</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6" s="3">
+        <v>754.12900000000002</v>
+      </c>
+      <c r="I6" s="3">
+        <v>752.93499999999995</v>
+      </c>
+      <c r="J6" s="3">
+        <v>599.57100000000003</v>
+      </c>
+      <c r="K6" s="3">
+        <v>673.96199999999999</v>
+      </c>
+      <c r="L6" s="3">
+        <v>655.12800000000004</v>
+      </c>
+      <c r="M6" s="3">
+        <v>616.35299999999995</v>
+      </c>
+      <c r="N6">
+        <v>716.44500000000005</v>
+      </c>
+      <c r="O6">
+        <v>774.64499999999998</v>
+      </c>
+      <c r="P6">
+        <v>708.077</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
@@ -564,18 +769,57 @@
       <c r="D7">
         <v>926.91099999999994</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="3">
         <v>993.35699999999997</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="3">
         <v>838.85299999999995</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="3">
         <v>953.25699999999995</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7" s="3">
+        <v>981.51199999999994</v>
+      </c>
+      <c r="I7" s="3">
+        <v>990.84100000000001</v>
+      </c>
+      <c r="J7" s="3">
+        <v>827.923</v>
+      </c>
+      <c r="K7" s="3">
+        <v>946.64499999999998</v>
+      </c>
+      <c r="L7" s="3">
+        <v>909.56399999999996</v>
+      </c>
+      <c r="M7" s="3">
+        <v>850.56600000000003</v>
+      </c>
+      <c r="N7">
+        <v>1022.44</v>
+      </c>
+      <c r="O7">
+        <v>1082</v>
+      </c>
+      <c r="P7">
+        <v>949.03700000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B9" s="1"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
